--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>134704447</v>
       </c>
       <c r="B3" t="n">
-        <v>99082</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>134705462</v>
       </c>
       <c r="B137" t="n">
-        <v>98719</v>
+        <v>98959</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>134704447</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>134705462</v>
       </c>
       <c r="B137" t="n">
-        <v>98959</v>
+        <v>98962</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
